--- a/03_Outputs/all/01_TablasDescriptivas/idx11_pobreza.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx11_pobreza.xlsx
@@ -421,7 +421,7 @@
         <v>-16.55643611937943</v>
       </c>
       <c r="D3">
-        <v>8.392307655790971</v>
+        <v>8.392307655790972</v>
       </c>
       <c r="E3">
         <v>-38.6662364551147</v>
@@ -641,7 +641,7 @@
         <v>-5.063719909292788</v>
       </c>
       <c r="D13">
-        <v>4.456982884320932</v>
+        <v>4.456982884320933</v>
       </c>
       <c r="E13">
         <v>-20.1754818746989</v>
@@ -663,7 +663,7 @@
         <v>-5.974073793538715</v>
       </c>
       <c r="D14">
-        <v>4.809903292955462</v>
+        <v>4.809903292955461</v>
       </c>
       <c r="E14">
         <v>-20.0738192301841</v>
@@ -685,7 +685,7 @@
         <v>-14.13325338068828</v>
       </c>
       <c r="D15">
-        <v>7.591072809153482</v>
+        <v>7.591072809153483</v>
       </c>
       <c r="E15">
         <v>-36.861041919971</v>
@@ -707,7 +707,7 @@
         <v>-17.63472847279744</v>
       </c>
       <c r="D16">
-        <v>9.1225443174673</v>
+        <v>9.122544317467298</v>
       </c>
       <c r="E16">
         <v>-41.1822790404115</v>
@@ -729,7 +729,7 @@
         <v>-15.57870907232157</v>
       </c>
       <c r="D17">
-        <v>8.027109893421322</v>
+        <v>8.02710989342132</v>
       </c>
       <c r="E17">
         <v>-37.6388845572579</v>
